--- a/Resultados_Reales_Eliminatorias.xlsx
+++ b/Resultados_Reales_Eliminatorias.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="77">
   <si>
     <t>Fase</t>
   </si>
@@ -617,12 +617,18 @@
       <c r="C5" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D5" s="2">
+        <v>2</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
       <c r="F5" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="G5" s="3"/>
+      <c r="G5" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">

--- a/Resultados_Reales_Eliminatorias.xlsx
+++ b/Resultados_Reales_Eliminatorias.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="77">
   <si>
     <t>Fase</t>
   </si>
@@ -725,12 +725,18 @@
       <c r="C11" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
+      <c r="D11" s="2">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2">
+        <v>1</v>
+      </c>
       <c r="F11" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="G11" s="3"/>
+      <c r="G11" s="3" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">

--- a/Resultados_Reales_Eliminatorias.xlsx
+++ b/Resultados_Reales_Eliminatorias.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="77">
   <si>
     <t>Fase</t>
   </si>
@@ -256,7 +256,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -267,6 +267,13 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -290,11 +297,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -583,12 +591,18 @@
       <c r="C3" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
       <c r="F3" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="3"/>
+      <c r="G3" s="4" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">

--- a/Resultados_Reales_Eliminatorias.xlsx
+++ b/Resultados_Reales_Eliminatorias.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="77">
   <si>
     <t>Fase</t>
   </si>
@@ -722,12 +722,18 @@
       <c r="C10" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2">
+        <v>2</v>
+      </c>
       <c r="F10" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="G10" s="3"/>
+      <c r="G10" s="3" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
@@ -762,12 +768,18 @@
       <c r="C12" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
+      <c r="D12" s="2">
+        <v>3</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
       <c r="F12" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="G12" s="3"/>
+      <c r="G12" s="3" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
@@ -866,7 +878,9 @@
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="2"/>
-      <c r="F18" s="3"/>
+      <c r="F18" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="G18" s="3"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
@@ -889,10 +903,14 @@
       <c r="B20" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="3"/>
+      <c r="C20" s="3" t="s">
+        <v>51</v>
+      </c>
       <c r="D20" s="3"/>
       <c r="E20" s="2"/>
-      <c r="F20" s="3"/>
+      <c r="F20" s="3" t="s">
+        <v>63</v>
+      </c>
       <c r="G20" s="3"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
@@ -954,10 +972,14 @@
       <c r="B25" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="3"/>
+      <c r="C25" s="3" t="s">
+        <v>64</v>
+      </c>
       <c r="D25" s="3"/>
       <c r="E25" s="2"/>
-      <c r="F25" s="3"/>
+      <c r="F25" s="3" t="s">
+        <v>65</v>
+      </c>
       <c r="G25" s="3"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">

--- a/Resultados_Reales_Eliminatorias.xlsx
+++ b/Resultados_Reales_Eliminatorias.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="77">
   <si>
     <t>Fase</t>
   </si>
@@ -705,12 +705,18 @@
       <c r="C9" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
+      <c r="D9" s="2">
+        <v>2</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
       <c r="F9" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="G9" s="3"/>
+      <c r="G9" s="3" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
@@ -946,7 +952,9 @@
       <c r="B23" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="3"/>
+      <c r="C23" s="3" t="s">
+        <v>56</v>
+      </c>
       <c r="D23" s="3"/>
       <c r="E23" s="2"/>
       <c r="F23" s="3"/>

--- a/Resultados_Reales_Eliminatorias.xlsx
+++ b/Resultados_Reales_Eliminatorias.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="78">
   <si>
     <t>Fase</t>
   </si>
@@ -250,6 +250,9 @@
   </si>
   <si>
     <t>Ghana</t>
+  </si>
+  <si>
+    <t>Bélgica</t>
   </si>
 </sst>
 </file>
@@ -614,12 +617,18 @@
       <c r="C4" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
+      <c r="D4" s="2">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
       <c r="F4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G4" s="3"/>
+      <c r="G4" s="3" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
@@ -831,12 +840,18 @@
       <c r="C15" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
+      <c r="D15" s="2">
+        <v>3</v>
+      </c>
+      <c r="E15" s="2">
+        <v>2</v>
+      </c>
       <c r="F15" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="G15" s="3"/>
+      <c r="G15" s="3" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -848,12 +863,18 @@
       <c r="C16" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
+      <c r="D16" s="2">
+        <v>2</v>
+      </c>
+      <c r="E16" s="2">
+        <v>1</v>
+      </c>
       <c r="F16" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G16" s="3"/>
+      <c r="G16" s="3" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">

--- a/Resultados_Reales_Eliminatorias.xlsx
+++ b/Resultados_Reales_Eliminatorias.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="78">
   <si>
     <t>Fase</t>
   </si>
@@ -917,10 +917,14 @@
       <c r="B19" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="3"/>
+      <c r="C19" s="3" t="s">
+        <v>49</v>
+      </c>
       <c r="D19" s="3"/>
       <c r="E19" s="2"/>
-      <c r="F19" s="3"/>
+      <c r="F19" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="G19" s="3"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
@@ -978,7 +982,9 @@
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="2"/>
-      <c r="F23" s="3"/>
+      <c r="F23" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="G23" s="3"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">

--- a/Resultados_Reales_Eliminatorias.xlsx
+++ b/Resultados_Reales_Eliminatorias.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="78">
   <si>
     <t>Fase</t>
   </si>
@@ -806,12 +806,18 @@
       <c r="C13" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
+      <c r="D13" s="2">
+        <v>2</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1</v>
+      </c>
       <c r="F13" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="G13" s="3"/>
+      <c r="G13" s="3" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -823,12 +829,18 @@
       <c r="C14" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
+      <c r="D14" s="2">
+        <v>3</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
       <c r="F14" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="G14" s="3"/>
+      <c r="G14" s="3" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
@@ -994,10 +1006,14 @@
       <c r="B24" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="3"/>
+      <c r="C24" s="3" t="s">
+        <v>67</v>
+      </c>
       <c r="D24" s="3"/>
       <c r="E24" s="2"/>
-      <c r="F24" s="3"/>
+      <c r="F24" s="3" t="s">
+        <v>69</v>
+      </c>
       <c r="G24" s="3"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">

--- a/Resultados_Reales_Eliminatorias.xlsx
+++ b/Resultados_Reales_Eliminatorias.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="78">
   <si>
     <t>Fase</t>
   </si>
@@ -680,12 +680,18 @@
       <c r="C7" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="D7" s="2">
+        <v>2</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
       <c r="F7" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="G7" s="3"/>
+      <c r="G7" s="3" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -976,7 +982,9 @@
       <c r="B22" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="3"/>
+      <c r="C22" s="3" t="s">
+        <v>54</v>
+      </c>
       <c r="D22" s="3"/>
       <c r="E22" s="2"/>
       <c r="F22" s="3"/>

--- a/Resultados_Reales_Eliminatorias.xlsx
+++ b/Resultados_Reales_Eliminatorias.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="78">
   <si>
     <t>Fase</t>
   </si>
@@ -663,12 +663,18 @@
       <c r="C6" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="D6" s="2">
+        <v>3</v>
+      </c>
+      <c r="E6" s="2">
+        <v>2</v>
+      </c>
       <c r="F6" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G6" s="3"/>
+      <c r="G6" s="3" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
@@ -703,12 +709,18 @@
       <c r="C8" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1</v>
+      </c>
       <c r="F8" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="G8" s="3"/>
+      <c r="G8" s="3" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
@@ -904,12 +916,18 @@
       <c r="C17" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
+      <c r="D17" s="2">
+        <v>1</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
       <c r="F17" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G17" s="3"/>
+      <c r="G17" s="3" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -969,10 +987,14 @@
       <c r="B21" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="3"/>
+      <c r="C21" s="3" t="s">
+        <v>53</v>
+      </c>
       <c r="D21" s="3"/>
       <c r="E21" s="2"/>
-      <c r="F21" s="3"/>
+      <c r="F21" s="3" t="s">
+        <v>61</v>
+      </c>
       <c r="G21" s="3"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
@@ -987,7 +1009,9 @@
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="2"/>
-      <c r="F22" s="3"/>
+      <c r="F22" s="3" t="s">
+        <v>75</v>
+      </c>
       <c r="G22" s="3"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">

--- a/Resultados_Reales_Eliminatorias.xlsx
+++ b/Resultados_Reales_Eliminatorias.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="78">
   <si>
     <t>Fase</t>
   </si>
@@ -939,12 +939,18 @@
       <c r="C18" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="2"/>
+      <c r="D18" s="3">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2">
+        <v>3</v>
+      </c>
       <c r="F18" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G18" s="3"/>
+      <c r="G18" s="3" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
@@ -973,12 +979,18 @@
       <c r="C20" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="2"/>
+      <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2">
+        <v>2</v>
+      </c>
       <c r="F20" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G20" s="3"/>
+      <c r="G20" s="3" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
@@ -1058,12 +1070,18 @@
       <c r="C25" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D25" s="3"/>
-      <c r="E25" s="2"/>
+      <c r="D25" s="3">
+        <v>0</v>
+      </c>
+      <c r="E25" s="2">
+        <v>1</v>
+      </c>
       <c r="F25" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="G25" s="3"/>
+      <c r="G25" s="3" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">

--- a/Resultados_Reales_Eliminatorias.xlsx
+++ b/Resultados_Reales_Eliminatorias.xlsx
@@ -980,7 +980,7 @@
         <v>51</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="2">
         <v>2</v>

--- a/Resultados_Reales_Eliminatorias.xlsx
+++ b/Resultados_Reales_Eliminatorias.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="78">
   <si>
     <t>Fase</t>
   </si>
@@ -1036,12 +1036,18 @@
       <c r="C23" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D23" s="3"/>
-      <c r="E23" s="2"/>
+      <c r="D23" s="3">
+        <v>2</v>
+      </c>
+      <c r="E23" s="2">
+        <v>3</v>
+      </c>
       <c r="F23" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="G23" s="3"/>
+      <c r="G23" s="3" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">

--- a/Resultados_Reales_Eliminatorias.xlsx
+++ b/Resultados_Reales_Eliminatorias.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="78">
   <si>
     <t>Fase</t>
   </si>
@@ -1059,12 +1059,18 @@
       <c r="C24" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="2"/>
+      <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="2">
+        <v>1</v>
+      </c>
       <c r="F24" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="G24" s="3"/>
+      <c r="G24" s="3" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">

--- a/Resultados_Reales_Eliminatorias.xlsx
+++ b/Resultados_Reales_Eliminatorias.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="78">
   <si>
     <t>Fase</t>
   </si>
@@ -962,12 +962,18 @@
       <c r="C19" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="2"/>
+      <c r="D19" s="3">
+        <v>1</v>
+      </c>
+      <c r="E19" s="2">
+        <v>4</v>
+      </c>
       <c r="F19" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="G19" s="3"/>
+      <c r="G19" s="3" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">

--- a/Resultados_Reales_Eliminatorias.xlsx
+++ b/Resultados_Reales_Eliminatorias.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="78">
   <si>
     <t>Fase</t>
   </si>
@@ -1108,10 +1108,14 @@
       <c r="B26" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="2"/>
+      <c r="C26" s="2" t="s">
+        <v>65</v>
+      </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
+      <c r="F26" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="G26" s="3"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
@@ -1121,10 +1125,14 @@
       <c r="B27" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C27" s="2"/>
+      <c r="C27" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
+      <c r="F27" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="G27" s="3"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
@@ -1134,10 +1142,14 @@
       <c r="B28" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C28" s="2"/>
+      <c r="C28" s="2" t="s">
+        <v>63</v>
+      </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
+      <c r="F28" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="G28" s="3"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">

--- a/Resultados_Reales_Eliminatorias.xlsx
+++ b/Resultados_Reales_Eliminatorias.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="78">
   <si>
     <t>Fase</t>
   </si>
@@ -1008,12 +1008,18 @@
       <c r="C21" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="2"/>
+      <c r="D21" s="3">
+        <v>3</v>
+      </c>
+      <c r="E21" s="2">
+        <v>2</v>
+      </c>
       <c r="F21" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="G21" s="3"/>
+      <c r="G21" s="3" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -1025,12 +1031,18 @@
       <c r="C22" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="2"/>
+      <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0</v>
+      </c>
       <c r="F22" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="G22" s="3"/>
+      <c r="G22" s="3" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
@@ -1159,10 +1171,14 @@
       <c r="B29" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C29" s="2"/>
+      <c r="C29" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
-      <c r="F29" s="3"/>
+      <c r="F29" s="3" t="s">
+        <v>54</v>
+      </c>
       <c r="G29" s="3"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">

--- a/Resultados_Reales_Eliminatorias.xlsx
+++ b/Resultados_Reales_Eliminatorias.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="78">
   <si>
     <t>Fase</t>
   </si>
@@ -1123,12 +1123,18 @@
       <c r="C26" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
+      <c r="D26" s="2">
+        <v>2</v>
+      </c>
+      <c r="E26" s="2">
+        <v>0</v>
+      </c>
       <c r="F26" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="G26" s="3"/>
+      <c r="G26" s="3" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
@@ -1140,12 +1146,18 @@
       <c r="C27" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
+      <c r="D27" s="2">
+        <v>2</v>
+      </c>
+      <c r="E27" s="2">
+        <v>1</v>
+      </c>
       <c r="F27" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="G27" s="3"/>
+      <c r="G27" s="3" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
@@ -1188,10 +1200,14 @@
       <c r="B30" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C30" s="2"/>
+      <c r="C30" s="2" t="s">
+        <v>65</v>
+      </c>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
+      <c r="F30" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="G30" s="3"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">

--- a/Resultados_Reales_Eliminatorias.xlsx
+++ b/Resultados_Reales_Eliminatorias.xlsx
@@ -162,9 +162,6 @@
     <t>Canadá</t>
   </si>
   <si>
-    <t>Paises Bajos</t>
-  </si>
-  <si>
     <t>Marruecos</t>
   </si>
   <si>
@@ -253,6 +250,9 @@
   </si>
   <si>
     <t>Bélgica</t>
+  </si>
+  <si>
+    <t>Países Bajos</t>
   </si>
 </sst>
 </file>
@@ -592,19 +592,19 @@
         <v>9</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D3" s="2">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="G3" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -615,19 +615,19 @@
         <v>10</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="2">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="2">
-        <v>2</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="G4" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -638,19 +638,19 @@
         <v>11</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="2">
+        <v>2</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D5" s="2">
-        <v>2</v>
-      </c>
-      <c r="E5" s="2">
-        <v>1</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="G5" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -661,7 +661,7 @@
         <v>12</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D6" s="2">
         <v>3</v>
@@ -670,10 +670,10 @@
         <v>2</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -684,7 +684,7 @@
         <v>13</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D7" s="2">
         <v>2</v>
@@ -693,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -707,7 +707,7 @@
         <v>14</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>
@@ -716,10 +716,10 @@
         <v>1</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -730,7 +730,7 @@
         <v>15</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D9" s="2">
         <v>2</v>
@@ -739,10 +739,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -753,7 +753,7 @@
         <v>16</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D10" s="2">
         <v>1</v>
@@ -762,10 +762,10 @@
         <v>2</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -776,7 +776,7 @@
         <v>17</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D11" s="2">
         <v>1</v>
@@ -785,10 +785,10 @@
         <v>1</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -799,7 +799,7 @@
         <v>18</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D12" s="2">
         <v>3</v>
@@ -808,10 +808,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -822,19 +822,19 @@
         <v>19</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" s="2">
+        <v>2</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D13" s="2">
-        <v>2</v>
-      </c>
-      <c r="E13" s="2">
-        <v>1</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="G13" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -845,7 +845,7 @@
         <v>20</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D14" s="2">
         <v>3</v>
@@ -854,10 +854,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -868,7 +868,7 @@
         <v>21</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D15" s="2">
         <v>3</v>
@@ -877,10 +877,10 @@
         <v>2</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -891,19 +891,19 @@
         <v>22</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D16" s="2">
+        <v>2</v>
+      </c>
+      <c r="E16" s="2">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D16" s="2">
-        <v>2</v>
-      </c>
-      <c r="E16" s="2">
-        <v>1</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="G16" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
@@ -914,19 +914,19 @@
         <v>23</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D17" s="2">
+        <v>1</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D17" s="2">
-        <v>1</v>
-      </c>
-      <c r="E17" s="2">
-        <v>0</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="G17" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
@@ -946,10 +946,10 @@
         <v>3</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
@@ -960,7 +960,7 @@
         <v>26</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D19" s="3">
         <v>1</v>
@@ -969,10 +969,10 @@
         <v>4</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
@@ -983,7 +983,7 @@
         <v>27</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D20" s="3">
         <v>1</v>
@@ -992,10 +992,10 @@
         <v>2</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
@@ -1006,7 +1006,7 @@
         <v>28</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D21" s="3">
         <v>3</v>
@@ -1015,10 +1015,10 @@
         <v>2</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
@@ -1029,7 +1029,7 @@
         <v>29</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D22" s="3">
         <v>0</v>
@@ -1038,10 +1038,10 @@
         <v>0</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
@@ -1052,7 +1052,7 @@
         <v>30</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D23" s="3">
         <v>2</v>
@@ -1061,10 +1061,10 @@
         <v>3</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
@@ -1075,7 +1075,7 @@
         <v>31</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D24" s="3">
         <v>0</v>
@@ -1084,10 +1084,10 @@
         <v>1</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
@@ -1098,19 +1098,19 @@
         <v>32</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D25" s="3">
+        <v>0</v>
+      </c>
+      <c r="E25" s="2">
+        <v>1</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D25" s="3">
-        <v>0</v>
-      </c>
-      <c r="E25" s="2">
-        <v>1</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="G25" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
@@ -1121,7 +1121,7 @@
         <v>34</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D26" s="2">
         <v>2</v>
@@ -1130,10 +1130,10 @@
         <v>0</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
@@ -1144,7 +1144,7 @@
         <v>35</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D27" s="2">
         <v>2</v>
@@ -1153,10 +1153,10 @@
         <v>1</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
@@ -1167,12 +1167,12 @@
         <v>36</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
       <c r="F28" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G28" s="3"/>
     </row>
@@ -1184,12 +1184,12 @@
         <v>37</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
       <c r="F29" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G29" s="3"/>
     </row>
@@ -1201,12 +1201,12 @@
         <v>39</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
       <c r="F30" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G30" s="3"/>
     </row>

--- a/Resultados_Reales_Eliminatorias.xlsx
+++ b/Resultados_Reales_Eliminatorias.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="78">
   <si>
     <t>Fase</t>
   </si>
@@ -1169,12 +1169,18 @@
       <c r="C28" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
+      <c r="D28" s="2">
+        <v>1</v>
+      </c>
+      <c r="E28" s="2">
+        <v>2</v>
+      </c>
       <c r="F28" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="G28" s="3"/>
+      <c r="G28" s="3" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
@@ -1186,12 +1192,18 @@
       <c r="C29" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
+      <c r="D29" s="2">
+        <v>3</v>
+      </c>
+      <c r="E29" s="2">
+        <v>1</v>
+      </c>
       <c r="F29" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G29" s="3"/>
+      <c r="G29" s="3" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
@@ -1217,10 +1229,14 @@
       <c r="B31" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C31" s="2"/>
+      <c r="C31" s="2" t="s">
+        <v>72</v>
+      </c>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
+      <c r="F31" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="G31" s="3"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">

--- a/Resultados_Reales_Eliminatorias.xlsx
+++ b/Resultados_Reales_Eliminatorias.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="78">
   <si>
     <t>Fase</t>
   </si>
@@ -1215,12 +1215,18 @@
       <c r="C30" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
+      <c r="D30" s="2">
+        <v>0</v>
+      </c>
+      <c r="E30" s="2">
+        <v>2</v>
+      </c>
       <c r="F30" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="G30" s="3"/>
+      <c r="G30" s="3" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
@@ -1232,12 +1238,18 @@
       <c r="C31" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
+      <c r="D31" s="2">
+        <v>1</v>
+      </c>
+      <c r="E31" s="2">
+        <v>2</v>
+      </c>
       <c r="F31" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="G31" s="3"/>
+      <c r="G31" s="3" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
@@ -1246,10 +1258,14 @@
       <c r="B32" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C32" s="2"/>
+      <c r="C32" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
+      <c r="F32" s="2" t="s">
+        <v>72</v>
+      </c>
       <c r="G32" s="3"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
@@ -1259,10 +1275,14 @@
       <c r="B33" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C33" s="2"/>
+      <c r="C33" s="2" t="s">
+        <v>68</v>
+      </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
+      <c r="F33" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="G33" s="3"/>
     </row>
   </sheetData>

--- a/Resultados_Reales_Eliminatorias.xlsx
+++ b/Resultados_Reales_Eliminatorias.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="78">
   <si>
     <t>Fase</t>
   </si>
@@ -1261,12 +1261,18 @@
       <c r="C32" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
+      <c r="D32" s="2">
+        <v>4</v>
+      </c>
+      <c r="E32" s="2">
+        <v>6</v>
+      </c>
       <c r="F32" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="G32" s="3"/>
+      <c r="G32" s="3" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
@@ -1278,12 +1284,18 @@
       <c r="C33" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
+      <c r="D33" s="2">
+        <v>1</v>
+      </c>
+      <c r="E33" s="2">
+        <v>0</v>
+      </c>
       <c r="F33" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="G33" s="3"/>
+      <c r="G33" s="3" t="s">
+        <v>68</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
